--- a/backend/data/financials_by_company/000683.SZ.xlsx
+++ b/backend/data/financials_by_company/000683.SZ.xlsx
@@ -3425,7 +3425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FB2"/>
+  <dimension ref="A1:EZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3866,355 +3866,345 @@
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>recommendationMean</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>numberOfAnalystOpinions</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>numberOfAnalystOpinions</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DK1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DL1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DM1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>longName</t>
         </is>
       </c>
       <c r="DN1" t="inlineStr">
         <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
       <c r="EZ1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4301,7 +4291,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Zhanfei  Xing', 'age': 52, 'title': 'GM &amp; Director', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jun  Li', 'age': 38, 'title': 'Financial Director', 'yearBorn': 1987, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yu Ying  Ma', 'age': 46, 'title': 'Chief Accountant', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yuhu  Ji', 'age': 51, 'title': 'Deputy General Manager', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yanhua  Wang', 'age': 48, 'title': 'Chief Engineer &amp; Director', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yang  Hua', 'age': 48, 'title': 'Deputy GM &amp; Board Secretary', 'yearBorn': 1977, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yuan  Gao', 'age': 47, 'title': 'Deputy General Manager', 'yearBorn': 1978, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peng Cheng  Dai', 'age': 41, 'title': 'Deputy General Manager', 'yearBorn': 1984, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiang  Lu', 'age': 53, 'title': 'Head of Internal Control', 'yearBorn': 1972, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jiawei  Wang', 'title': 'Board Secretary', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -4316,70 +4306,70 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="V2" t="n">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="W2" t="n">
-        <v>6.17</v>
+        <v>5.92</v>
       </c>
       <c r="X2" t="n">
-        <v>6.57</v>
+        <v>6.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.29</v>
+        <v>6.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.56</v>
+        <v>6.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.17</v>
+        <v>5.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.57</v>
+        <v>6.09</v>
       </c>
       <c r="AC2" t="n">
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.42</v>
+        <v>4.96</v>
       </c>
       <c r="AE2" t="n">
-        <v>1750118400</v>
+        <v>1783382400</v>
       </c>
       <c r="AF2" t="n">
         <v>1.1111</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.539</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>24.185184</v>
+        <v>22.296295</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.046155</v>
+        <v>9.2615385</v>
       </c>
       <c r="AJ2" t="n">
-        <v>150169463</v>
+        <v>68295600</v>
       </c>
       <c r="AK2" t="n">
-        <v>150169463</v>
+        <v>68295600</v>
       </c>
       <c r="AL2" t="n">
-        <v>45275164</v>
+        <v>51461250</v>
       </c>
       <c r="AM2" t="n">
-        <v>57121420</v>
+        <v>83339394</v>
       </c>
       <c r="AN2" t="n">
-        <v>57121420</v>
+        <v>83339394</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.49</v>
+        <v>6.01</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.5</v>
+        <v>6.02</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4388,13 +4378,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>24270909440</v>
+        <v>22375325696</v>
       </c>
       <c r="AT2" t="n">
-        <v>23378870512</v>
+        <v>21743464626</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.72</v>
+        <v>4.79</v>
       </c>
       <c r="AV2" t="n">
         <v>10</v>
@@ -4406,19 +4396,19 @@
         <v>0.703703</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.0354495</v>
+        <v>1.8764787</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.9666</v>
+        <v>7.5052</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.66</v>
+        <v>7.6538</v>
       </c>
       <c r="BB2" t="n">
         <v>0.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.047694758</v>
+        <v>0.049586777</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4429,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>40544649216</v>
+        <v>38596952064</v>
       </c>
       <c r="BG2" t="n">
         <v>0.0858</v>
@@ -4441,10 +4431,10 @@
         <v>3716831560</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.31847998</v>
+        <v>0.31683</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.21172</v>
+        <v>0.20124</v>
       </c>
       <c r="BL2" t="n">
         <v>3716831560</v>
@@ -4453,7 +4443,7 @@
         <v>3.41</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.914956</v>
+        <v>1.7653959</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4485,22 +4475,22 @@
         <v>1463011200</v>
       </c>
       <c r="BX2" t="n">
-        <v>3.4</v>
+        <v>3.237</v>
       </c>
       <c r="BY2" t="n">
-        <v>10.235</v>
+        <v>9.744</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.32421052</v>
+        <v>0.2577963</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CB2" t="n">
         <v>0.3</v>
       </c>
       <c r="CC2" t="n">
-        <v>1750118400</v>
+        <v>1783382400</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4508,7 +4498,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>6.53</v>
+        <v>6.02</v>
       </c>
       <c r="CF2" t="n">
         <v>10.5</v>
@@ -4522,259 +4512,251 @@
       <c r="CI2" t="n">
         <v>10.5</v>
       </c>
-      <c r="CJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK2" t="inlineStr">
-        <is>
-          <t>strong_buy</t>
-        </is>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CK2" t="n">
+        <v>2</v>
       </c>
       <c r="CL2" t="n">
-        <v>2</v>
+        <v>1508298880</v>
       </c>
       <c r="CM2" t="n">
-        <v>1508298880</v>
+        <v>0.395</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.395</v>
+        <v>3961260032</v>
       </c>
       <c r="CO2" t="n">
-        <v>3961260032</v>
+        <v>13177167872</v>
       </c>
       <c r="CP2" t="n">
-        <v>13177167872</v>
+        <v>0.153</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.153</v>
+        <v>0.346</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.346</v>
+        <v>11924103168</v>
       </c>
       <c r="CS2" t="n">
-        <v>11924103168</v>
+        <v>77.68899999999999</v>
       </c>
       <c r="CT2" t="n">
-        <v>77.68899999999999</v>
+        <v>3.218</v>
       </c>
       <c r="CU2" t="n">
-        <v>3.218</v>
+        <v>0.037920002</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.037920002</v>
+        <v>0.08254</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.08254</v>
+        <v>3618444032</v>
       </c>
       <c r="CX2" t="n">
-        <v>3618444032</v>
+        <v>2087036928</v>
       </c>
       <c r="CY2" t="n">
-        <v>2087036928</v>
+        <v>2334821888</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2334821888</v>
+        <v>0.222</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.222</v>
+        <v>-0.052</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0.052</v>
+        <v>0.30346</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.30346</v>
+        <v>0.33221</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.33221</v>
-      </c>
-      <c r="DE2" t="n">
         <v>0.21697001</v>
       </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>000683.SZ</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>000683.SZ</t>
+          <t>en-US</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>en-US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DL2" t="b">
+      <c r="DK2" t="b">
         <v>0</v>
       </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
+          <t>Inner Mongolia Berun Chemical Company Limited</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.03000021</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>5.92 - 6.09</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>51461250</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.25678498</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>4.79 - 10.0</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.398</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>25.779629</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1651143540</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1651233600</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>10.945455</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>INNER MONGOLIA BERUN CHEMICAL C</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>[{'header': 'Dividend', 'message': '000683.SZ announced a cash dividend of CNY 0.30 with an ex-date of Jul. 7, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1783353600000, 'amount': '0.30'}}]</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>1783062267</v>
+      </c>
+      <c r="EG2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>finmb_6480331</t>
         </is>
       </c>
-      <c r="DP2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DR2" t="n">
+      <c r="EK2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DT2" t="b">
+      <c r="EM2" t="b">
         <v>0</v>
       </c>
-      <c r="DU2" t="n">
-        <v>3.8155842</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DX2" t="n">
-        <v>1782111873</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>INNER MONGOLIA BERUN CHEMICAL C</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Inner Mongolia Berun Chemical Company Limited</t>
-        </is>
-      </c>
-      <c r="EB2" t="b">
+      <c r="EN2" t="n">
+        <v>-0.49587122</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-1.4851999</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.19788946</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-1.6338</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-0.21346259</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EW2" t="b">
         <v>0</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EY2" t="n">
         <v>854674200000</v>
       </c>
-      <c r="ED2" t="n">
-        <v>0.24000025</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>6.17 - 6.57</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EG2" t="n">
-        <v>45275164</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1.8100004</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.38347468</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>4.72 - 10.0</t>
-        </is>
-      </c>
-      <c r="EK2" t="n">
-        <v>-3.4699998</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.34699997</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>32.42105</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>1651143540</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>1651233600</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>11.872727</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-1.4365997</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>-0.18032783</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>-1.1299996</v>
-      </c>
-      <c r="EW2" t="n">
-        <v>-0.14751954</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EZ2" t="inlineStr">
-        <is>
-          <t>1.0 - Strong Buy</t>
-        </is>
-      </c>
-      <c r="FA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FB2" t="inlineStr"/>
+      <c r="EZ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
